--- a/data/trans_camb/P15A-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,8</t>
+          <t>-2,22; 3,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,52</t>
+          <t>-3,86; 0,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,69</t>
+          <t>-3,59; 1,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 2,57</t>
+          <t>-3,24; 2,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 3,47</t>
+          <t>-3,07; 3,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 4,06</t>
+          <t>-1,43; 3,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,49</t>
+          <t>-1,89; 2,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,61</t>
+          <t>-2,55; 1,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,96</t>
+          <t>-1,59; 2,08</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 184,36</t>
+          <t>-48,63; 175,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,31; 98,37</t>
+          <t>-84,07; 72,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 103,32</t>
+          <t>-73,77; 88,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-79,13; 213,85</t>
+          <t>-79,39; 223,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,44; 305,58</t>
+          <t>-74,43; 232,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 353,47</t>
+          <t>-38,98; 319,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 127,31</t>
+          <t>-49,53; 125,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,72; 80,88</t>
+          <t>-61,49; 72,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 97,86</t>
+          <t>-38,44; 110,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,36</t>
+          <t>-1,13; 2,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,25</t>
+          <t>-1,97; 1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,05</t>
+          <t>-1,07; 3,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,21</t>
+          <t>-2,12; 1,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,44</t>
+          <t>-2,66; 0,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,17</t>
+          <t>-0,23; 3,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,4</t>
+          <t>-1,11; 1,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,29</t>
+          <t>-1,82; 0,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,44</t>
+          <t>-0,23; 2,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,53; 299,93</t>
+          <t>-53,75; 355,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,79; 190,44</t>
+          <t>-83,19; 185,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,67; 379,95</t>
+          <t>-57,58; 414,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-73,55; 149,4</t>
+          <t>-77,77; 101,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,75; 61,89</t>
+          <t>-89,95; 84,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 312,06</t>
+          <t>-14,92; 357,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 127,44</t>
+          <t>-48,12; 123,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,3; 29,57</t>
+          <t>-73,43; 45,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 211,79</t>
+          <t>-16,38; 231,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 2,16</t>
+          <t>-4,87; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 1,63</t>
+          <t>-5,37; 1,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; -0,89</t>
+          <t>-7,29; -0,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,75</t>
+          <t>1,2; 7,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,37</t>
+          <t>-1,38; 2,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,0</t>
+          <t>-0,51; 3,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,8</t>
+          <t>-1,03; 3,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,42</t>
+          <t>-2,85; 1,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,63</t>
+          <t>-3,12; 0,42</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 56,6</t>
+          <t>-60,98; 64,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 50,73</t>
+          <t>-67,93; 44,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,78; -14,01</t>
+          <t>-88,63; -17,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,69; 1665,95</t>
+          <t>18,26; 1451,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 575,26</t>
+          <t>-79,03; 500,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 744,76</t>
+          <t>-31,24; 850,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 151,68</t>
+          <t>-26,42; 139,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,08; 68,27</t>
+          <t>-56,93; 53,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 27,25</t>
+          <t>-66,07; 21,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,08</t>
+          <t>-4,29; 2,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,59</t>
+          <t>-3,41; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 1,06</t>
+          <t>-5,58; 1,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,31</t>
+          <t>-2,95; 1,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,18</t>
+          <t>-0,62; 5,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,18</t>
+          <t>-3,23; 1,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,8</t>
+          <t>-2,74; 0,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,16</t>
+          <t>-1,14; 3,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,15</t>
+          <t>-3,85; 0,16</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,95; 60,11</t>
+          <t>-67,56; 64,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,86; 74,85</t>
+          <t>-53,53; 80,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,09; 53,86</t>
+          <t>-89,6; 85,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-78,56; 108,69</t>
+          <t>-76,48; 142,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 314,78</t>
+          <t>-24,76; 356,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,27; 129,95</t>
+          <t>-84,12; 114,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-62,99; 28,71</t>
+          <t>-58,81; 37,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 116,57</t>
+          <t>-25,69; 114,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-84,04; 16,46</t>
+          <t>-82,67; 18,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 3,04</t>
+          <t>-3,67; 3,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1,94</t>
+          <t>-4,5; 2,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 0,15</t>
+          <t>-5,89; 0,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,95</t>
+          <t>-3,23; 4,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 0,57</t>
+          <t>-5,66; 1,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,52; -1,51</t>
+          <t>-7,31; -1,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,52</t>
+          <t>-2,49; 2,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,45</t>
+          <t>-4,05; 0,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -1,22</t>
+          <t>-5,28; -1,29</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,17; 161,02</t>
+          <t>-70,85; 229,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-83,2; 135,76</t>
+          <t>-78,4; 133,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,75</t>
+          <t>-94,36; 93,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-66,21; 192,09</t>
+          <t>-65,82; 219,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 78,59</t>
+          <t>-91,67; 155,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 4,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 107,42</t>
+          <t>-50,79; 121,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-80,2; 25,75</t>
+          <t>-76,67; 41,02</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-95,88; -37,34</t>
+          <t>-96,41; -38,53</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 2,5</t>
+          <t>-3,9; 2,18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 6,51</t>
+          <t>-0,99; 6,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,39</t>
+          <t>-2,61; 3,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,88</t>
+          <t>-1,66; 6,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,43; 10,14</t>
+          <t>1,64; 10,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,17</t>
+          <t>-1,77; 4,34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,34</t>
+          <t>-1,75; 3,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,1</t>
+          <t>1,28; 7,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,18</t>
+          <t>-1,69; 2,65</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-79,4; 198,97</t>
+          <t>-77,63; 147,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 359,92</t>
+          <t>-25,54; 352,66</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 181,67</t>
+          <t>-56,8; 189,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 257,65</t>
+          <t>-33,1; 250,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13,33; 438,45</t>
+          <t>10,6; 437,54</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 178,28</t>
+          <t>-34,33; 206,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 141,72</t>
+          <t>-38,35; 129,55</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>21,18; 301,78</t>
+          <t>20,43; 286,87</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 138,15</t>
+          <t>-34,84; 111,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,17</t>
+          <t>-3,36; 1,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -1,46</t>
+          <t>-5,17; -1,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,23</t>
+          <t>-4,5; -0,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,64</t>
+          <t>-2,0; 1,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -0,69</t>
+          <t>-3,91; -0,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,16</t>
+          <t>-2,9; 1,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,83</t>
+          <t>-2,01; 0,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -1,45</t>
+          <t>-3,75; -1,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,04</t>
+          <t>-2,95; -0,06</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 40,23</t>
+          <t>-57,77; 44,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-89,52; -36,2</t>
+          <t>-89,34; -32,54</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-76,23; -2,73</t>
+          <t>-77,48; -5,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-53,04; 83,57</t>
+          <t>-50,36; 102,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-92,95; -19,83</t>
+          <t>-90,49; -6,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-69,96; 52,54</t>
+          <t>-69,17; 58,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 29,3</t>
+          <t>-45,05; 31,17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-87,24; -48,52</t>
+          <t>-85,38; -46,91</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-67,46; -4,06</t>
+          <t>-67,99; -0,93</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -0,72</t>
+          <t>-4,21; -0,87</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,63</t>
+          <t>-3,08; 0,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,01</t>
+          <t>-3,99; -0,31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,41; -0,2</t>
+          <t>-3,38; -0,1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,16</t>
+          <t>-3,17; -0,02</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,33; -0,04</t>
+          <t>-3,22; -0,11</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,93</t>
+          <t>-3,26; -0,96</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,34</t>
+          <t>-2,67; -0,31</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,01; -0,58</t>
+          <t>-3,05; -0,55</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-87,31; -23,43</t>
+          <t>-86,35; -21,12</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-64,57; 27,32</t>
+          <t>-64,72; 20,18</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 1,3</t>
+          <t>-83,51; -7,23</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-76,47; -1,82</t>
+          <t>-74,84; 3,36</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-74,16; -1,43</t>
+          <t>-74,8; 2,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-72,48; 3,25</t>
+          <t>-71,03; -2,24</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-76,29; -30,87</t>
+          <t>-75,24; -29,86</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-64,14; -8,98</t>
+          <t>-63,03; -8,79</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-72,5; -20,28</t>
+          <t>-73,24; -18,37</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,76; -0,02</t>
+          <t>-1,76; 0,02</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,33</t>
+          <t>-2,04; -0,25</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,74</t>
+          <t>-2,55; -0,7</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,8</t>
+          <t>-0,82; 0,76</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,52</t>
+          <t>-1,05; 0,4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,68</t>
+          <t>-1,18; 0,4</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,13</t>
+          <t>-1,06; 0,19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,41; -0,17</t>
+          <t>-1,31; -0,11</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,53; -0,32</t>
+          <t>-1,63; -0,36</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-41,63; -0,17</t>
+          <t>-41,18; 0,8</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-47,55; -8,93</t>
+          <t>-47,64; -7,48</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-60,25; -20,85</t>
+          <t>-60,78; -20,66</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 33,67</t>
+          <t>-26,77; 32,33</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 22,16</t>
+          <t>-33,81; 16,35</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 28,88</t>
+          <t>-34,88; 15,43</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 5,15</t>
+          <t>-29,33; 6,66</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-38,33; -5,57</t>
+          <t>-35,77; -2,64</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-43,6; -11,16</t>
+          <t>-45,66; -12,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15A-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,79</t>
+          <t>-2,24; 3,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,98</t>
+          <t>-3,92; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,66</t>
+          <t>-3,48; 2,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,73</t>
+          <t>-3,02; 2,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,17</t>
+          <t>-2,65; 3,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,92</t>
+          <t>-1,54; 3,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,36</t>
+          <t>-1,79; 2,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,52</t>
+          <t>-2,54; 1,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,08</t>
+          <t>-1,55; 2,2</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-25,37%</t>
+          <t>-19,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,63; 175,26</t>
+          <t>-51,65; 195,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,07; 72,42</t>
+          <t>-79,38; 81,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,77; 88,93</t>
+          <t>-68,06; 111,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-79,39; 223,19</t>
+          <t>-79,59; 244,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,43; 232,32</t>
+          <t>-66,55; 280,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 319,83</t>
+          <t>-34,5; 345,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 125,26</t>
+          <t>-45,48; 117,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,49; 72,28</t>
+          <t>-59,92; 78,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 110,41</t>
+          <t>-36,89; 113,04</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,36</t>
+          <t>-1,2; 2,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,19</t>
+          <t>-1,97; 1,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,35</t>
+          <t>-1,2; 3,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,02</t>
+          <t>-1,97; 1,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,29</t>
+          <t>-2,54; 0,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,14</t>
+          <t>-0,51; 2,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,36</t>
+          <t>-1,13; 1,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,43</t>
+          <t>-1,73; 0,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,55</t>
+          <t>-0,31; 2,25</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 355,81</t>
+          <t>-58,55; 259,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 185,71</t>
+          <t>-83,15; 134,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,58; 414,13</t>
+          <t>-54,9; 380,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,77; 101,18</t>
+          <t>-75,84; 124,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,95; 84,05</t>
+          <t>-91,55; 64,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 357,97</t>
+          <t>-19,62; 302,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 123,56</t>
+          <t>-52,26; 108,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,43; 45,82</t>
+          <t>-74,19; 41,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 231,46</t>
+          <t>-15,6; 206,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,2</t>
+          <t>-1,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,3</t>
+          <t>-4,34; 2,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,47</t>
+          <t>-5,36; 1,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -0,97</t>
+          <t>-7,24; -0,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,18</t>
+          <t>1,05; 6,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,29</t>
+          <t>-1,44; 2,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,08</t>
+          <t>-0,53; 2,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,5</t>
+          <t>-0,83; 3,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 1,1</t>
+          <t>-2,68; 1,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,42</t>
+          <t>-2,99; 0,69</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-68,09%</t>
+          <t>-61,78%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>106,72%</t>
+          <t>103,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-35,05%</t>
+          <t>-30,7%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,98; 64,62</t>
+          <t>-57,55; 70,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,93; 44,03</t>
+          <t>-66,58; 49,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-88,63; -17,87</t>
+          <t>-87,49; -12,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,26; 1451,1</t>
+          <t>14,52; 1338,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,03; 500,85</t>
+          <t>-75,76; 513,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 850,69</t>
+          <t>-36,43; 657,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 139,47</t>
+          <t>-23,54; 169,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,93; 53,7</t>
+          <t>-56,57; 57,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 21,86</t>
+          <t>-62,39; 31,94</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-0,9</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>-1,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,12</t>
+          <t>-4,36; 2,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 2,9</t>
+          <t>-3,55; 2,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,78</t>
+          <t>-5,2; 1,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,57</t>
+          <t>-3,34; 1,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,31</t>
+          <t>-0,42; 5,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,25</t>
+          <t>-2,93; 1,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,88</t>
+          <t>-3,0; 0,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,38</t>
+          <t>-1,17; 3,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,16</t>
+          <t>-3,61; 0,73</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-53,37%</t>
+          <t>-44,69%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,99%</t>
+          <t>-34,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-52,99%</t>
+          <t>-41,53%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,56; 64,26</t>
+          <t>-67,73; 67,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 80,33</t>
+          <t>-53,19; 81,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-89,6; 85,62</t>
+          <t>-83,73; 63,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 142,16</t>
+          <t>-80,16; 78,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 356,8</t>
+          <t>-13,4; 378,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-84,12; 114,72</t>
+          <t>-80,33; 131,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 37,25</t>
+          <t>-60,78; 30,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 114,79</t>
+          <t>-24,11; 103,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,67; 18,12</t>
+          <t>-76,06; 34,18</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>-2,42</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>-3,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,39</t>
+          <t>-3,9; 3,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,18</t>
+          <t>-4,78; 2,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,24</t>
+          <t>-5,56; 0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,02</t>
+          <t>-3,39; 4,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 1,03</t>
+          <t>-5,34; 1,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,31; -1,16</t>
+          <t>-6,96; -1,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,67</t>
+          <t>-2,6; 2,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,71</t>
+          <t>-4,02; 0,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -1,29</t>
+          <t>-5,46; -1,21</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-65,86%</t>
+          <t>-67,21%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-93,11%</t>
+          <t>-93,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-80,8%</t>
+          <t>-81,46%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,85; 229,62</t>
+          <t>-71,51; 206,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-78,4; 133,74</t>
+          <t>-80,16; 146,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-94,36; 93,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-65,82; 219,23</t>
+          <t>-62,47; 236,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-91,67; 155,57</t>
+          <t>-91,38; 144,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,59</t>
+          <t>-100,0; -8,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 121,47</t>
+          <t>-54,57; 111,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-76,67; 41,02</t>
+          <t>-78,93; 47,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-96,41; -38,53</t>
+          <t>-95,64; -44,23</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 2,18</t>
+          <t>-4,03; 2,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 6,14</t>
+          <t>-1,41; 6,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,16</t>
+          <t>-2,91; 2,79</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 6,05</t>
+          <t>-1,29; 6,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,17</t>
+          <t>1,33; 9,9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,34</t>
+          <t>-1,68; 4,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,18</t>
+          <t>-1,56; 3,37</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,07</t>
+          <t>1,3; 7,33</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,65</t>
+          <t>-1,66; 2,67</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-77,63; 147,86</t>
+          <t>-82,83; 157,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 352,66</t>
+          <t>-38,66; 343,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 189,97</t>
+          <t>-56,25; 161,92</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 250,42</t>
+          <t>-35,98; 287,56</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,6; 437,54</t>
+          <t>13,23; 445,75</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 206,06</t>
+          <t>-32,02; 212,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-38,35; 129,55</t>
+          <t>-36,31; 136,41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>20,43; 286,87</t>
+          <t>19,33; 294,35</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 111,58</t>
+          <t>-30,3; 111,02</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-1,02</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,2</t>
+          <t>-3,08; 1,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -1,33</t>
+          <t>-4,97; -1,12</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,32</t>
+          <t>-4,36; -0,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,78</t>
+          <t>-2,12; 1,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,91; -0,51</t>
+          <t>-3,78; -0,72</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,2</t>
+          <t>-1,68; 1,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,91</t>
+          <t>-1,99; 0,81</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -1,46</t>
+          <t>-3,83; -1,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,06</t>
+          <t>-2,33; 0,32</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-52,65%</t>
+          <t>-50,01%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-18,66%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-38,5%</t>
+          <t>-27,86%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 44,61</t>
+          <t>-56,64; 45,84</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-89,34; -32,54</t>
+          <t>-89,41; -35,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-77,48; -5,79</t>
+          <t>-74,93; -3,7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 102,84</t>
+          <t>-53,09; 81,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-90,49; -6,94</t>
+          <t>-92,05; -21,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-69,17; 58,74</t>
+          <t>-44,75; 94,95</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-45,05; 31,17</t>
+          <t>-43,68; 29,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-85,38; -46,91</t>
+          <t>-85,99; -45,67</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-67,99; -0,93</t>
+          <t>-53,02; 13,17</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>-1,5</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,21; -0,87</t>
+          <t>-4,08; -0,9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,31</t>
+          <t>-2,97; 0,7</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -0,31</t>
+          <t>-3,35; 0,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,1</t>
+          <t>-3,28; -0,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,17; -0,02</t>
+          <t>-3,35; -0,19</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,11</t>
+          <t>-3,41; -0,15</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -0,96</t>
+          <t>-3,32; -0,85</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,67; -0,31</t>
+          <t>-2,67; -0,34</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,55</t>
+          <t>-2,69; -0,29</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-53,72%</t>
+          <t>-39,8%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-46,4%</t>
+          <t>-46,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-50,47%</t>
+          <t>-43,01%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-86,35; -21,12</t>
+          <t>-86,3; -24,96</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-64,72; 20,18</t>
+          <t>-64,78; 29,71</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-83,51; -7,23</t>
+          <t>-70,92; 21,34</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-74,84; 3,36</t>
+          <t>-76,15; -6,47</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-74,8; 2,37</t>
+          <t>-73,34; -0,33</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-71,03; -2,24</t>
+          <t>-74,68; -1,81</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-75,24; -29,86</t>
+          <t>-77,0; -29,49</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-63,03; -8,79</t>
+          <t>-62,71; -9,14</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-73,24; -18,37</t>
+          <t>-64,65; -9,33</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,76</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,02</t>
+          <t>-1,75; -0,02</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,25</t>
+          <t>-2,05; -0,26</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,7</t>
+          <t>-2,34; -0,52</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,76</t>
+          <t>-0,78; 0,85</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,4</t>
+          <t>-1,11; 0,46</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,4</t>
+          <t>-0,89; 0,61</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,19</t>
+          <t>-1,04; 0,16</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,31; -0,11</t>
+          <t>-1,31; -0,18</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,63; -0,36</t>
+          <t>-1,31; -0,19</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-43,88%</t>
+          <t>-37,95%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-10,01%</t>
+          <t>-4,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-29,15%</t>
+          <t>-23,25%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 0,8</t>
+          <t>-41,01; -0,92</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-47,64; -7,48</t>
+          <t>-47,86; -7,2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-60,78; -20,66</t>
+          <t>-55,45; -15,64</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 32,33</t>
+          <t>-24,17; 36,3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 16,35</t>
+          <t>-34,57; 19,82</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 15,43</t>
+          <t>-27,6; 25,94</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 6,66</t>
+          <t>-28,88; 5,63</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-35,77; -2,64</t>
+          <t>-36,59; -5,73</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-45,66; -12,64</t>
+          <t>-36,74; -6,1</t>
         </is>
       </c>
     </row>
